--- a/artfynd/A 52631-2025 artfynd.xlsx
+++ b/artfynd/A 52631-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100309972</v>
+        <v>100307931</v>
       </c>
       <c r="B2" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2667</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535467.3422533221</v>
+        <v>535427</v>
       </c>
       <c r="R2" t="n">
-        <v>6431137.311909356</v>
+        <v>6431104</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2022-04-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-04-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,6 +774,311 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100309972</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Östorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>535467</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6431137</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100307919</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96458</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Östorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>535427</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6431104</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100310571</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56689</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Östorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>535430</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6431151</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52631-2025 artfynd.xlsx
+++ b/artfynd/A 52631-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100307931</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100309972</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100307919</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,8 +1099,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100310571</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>